--- a/excel/Libstar_Product_Report.xlsx
+++ b/excel/Libstar_Product_Report.xlsx
@@ -41,7 +41,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001B2A4A"/>
+      <color rgb="008E1E4D"/>
       <sz val="18"/>
     </font>
     <font>
@@ -51,7 +51,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001B2A4A"/>
+      <color rgb="008E1E4D"/>
       <sz val="14"/>
     </font>
     <font>
@@ -68,7 +68,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001B2A4A"/>
+      <color rgb="008E1E4D"/>
       <sz val="12"/>
     </font>
     <font>
@@ -96,12 +96,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001B2A4A"/>
+        <fgColor rgb="008E1E4D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF2F7"/>
+        <fgColor rgb="00FDF3F7"/>
       </patternFill>
     </fill>
   </fills>
